--- a/output/A股证券化率.xlsx
+++ b/output/A股证券化率.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,8 +17,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -10301,7 +10301,7 @@
         <v>45598</v>
       </c>
       <c r="B492" t="n">
-        <v>83.965</v>
+        <v>82.5339</v>
       </c>
       <c r="C492" t="n">
         <v>126.63</v>
@@ -10312,7 +10312,7 @@
         </is>
       </c>
       <c r="E492" t="n">
-        <v>66.31</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="F492" t="inlineStr"/>
     </row>
@@ -10321,7 +10321,7 @@
         <v>45613</v>
       </c>
       <c r="B493" t="n">
-        <v>86.6709</v>
+        <v>86.5774</v>
       </c>
       <c r="C493" t="n">
         <v>126.63</v>
@@ -10332,7 +10332,7 @@
         </is>
       </c>
       <c r="E493" t="n">
-        <v>68.44</v>
+        <v>68.37</v>
       </c>
       <c r="F493" t="inlineStr"/>
     </row>
@@ -10341,7 +10341,7 @@
         <v>45628</v>
       </c>
       <c r="B494" t="n">
-        <v>88.20310000000001</v>
+        <v>89.06999999999999</v>
       </c>
       <c r="C494" t="n">
         <v>126.63</v>
@@ -10352,7 +10352,7 @@
         </is>
       </c>
       <c r="E494" t="n">
-        <v>69.65000000000001</v>
+        <v>70.34</v>
       </c>
       <c r="F494" t="inlineStr"/>
     </row>
@@ -10361,7 +10361,7 @@
         <v>45643</v>
       </c>
       <c r="B495" t="n">
-        <v>88.0883</v>
+        <v>87.4524</v>
       </c>
       <c r="C495" t="n">
         <v>126.63</v>
@@ -10372,7 +10372,7 @@
         </is>
       </c>
       <c r="E495" t="n">
-        <v>69.56</v>
+        <v>69.06</v>
       </c>
       <c r="F495" t="inlineStr"/>
     </row>
@@ -10381,7 +10381,7 @@
         <v>45658</v>
       </c>
       <c r="B496" t="n">
-        <v>87.6399</v>
+        <v>84.9233</v>
       </c>
       <c r="C496" t="n">
         <v>126.63</v>
@@ -10392,7 +10392,7 @@
         </is>
       </c>
       <c r="E496" t="n">
-        <v>69.20999999999999</v>
+        <v>67.06</v>
       </c>
       <c r="F496" t="inlineStr"/>
     </row>
@@ -10401,7 +10401,7 @@
         <v>45673</v>
       </c>
       <c r="B497" t="n">
-        <v>82.307</v>
+        <v>80.1862</v>
       </c>
       <c r="C497" t="n">
         <v>126.63</v>
@@ -10412,7 +10412,7 @@
         </is>
       </c>
       <c r="E497" t="n">
-        <v>65</v>
+        <v>63.32</v>
       </c>
       <c r="F497" t="inlineStr"/>
     </row>
@@ -10421,7 +10421,7 @@
         <v>45688</v>
       </c>
       <c r="B498" t="n">
-        <v>82.97839999999999</v>
+        <v>80.6032</v>
       </c>
       <c r="C498" t="n">
         <v>134.91</v>
@@ -10432,7 +10432,7 @@
         </is>
       </c>
       <c r="E498" t="n">
-        <v>61.51</v>
+        <v>59.75</v>
       </c>
       <c r="F498" t="inlineStr"/>
     </row>
@@ -10441,7 +10441,7 @@
         <v>45703</v>
       </c>
       <c r="B499" t="n">
-        <v>87.40770000000001</v>
+        <v>87.8849</v>
       </c>
       <c r="C499" t="n">
         <v>134.91</v>
@@ -10452,7 +10452,7 @@
         </is>
       </c>
       <c r="E499" t="n">
-        <v>64.79000000000001</v>
+        <v>65.14</v>
       </c>
       <c r="F499" t="inlineStr"/>
     </row>
@@ -10461,7 +10461,7 @@
         <v>45718</v>
       </c>
       <c r="B500" t="n">
-        <v>86.2179</v>
+        <v>86.92619999999999</v>
       </c>
       <c r="C500" t="n">
         <v>134.91</v>
@@ -10472,7 +10472,7 @@
         </is>
       </c>
       <c r="E500" t="n">
-        <v>63.91</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="F500" t="inlineStr"/>
     </row>
@@ -10481,7 +10481,7 @@
         <v>45733</v>
       </c>
       <c r="B501" t="n">
-        <v>91.06699999999999</v>
+        <v>92.9876</v>
       </c>
       <c r="C501" t="n">
         <v>134.91</v>
@@ -10492,7 +10492,7 @@
         </is>
       </c>
       <c r="E501" t="n">
-        <v>67.5</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="F501" t="inlineStr"/>
     </row>
@@ -10501,7 +10501,7 @@
         <v>45748</v>
       </c>
       <c r="B502" t="n">
-        <v>87.48699999999999</v>
+        <v>87.0724</v>
       </c>
       <c r="C502" t="n">
         <v>134.91</v>
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="E502" t="n">
-        <v>64.84999999999999</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="F502" t="inlineStr"/>
     </row>
@@ -10521,7 +10521,7 @@
         <v>45763</v>
       </c>
       <c r="B503" t="n">
-        <v>84.1489</v>
+        <v>79.8874</v>
       </c>
       <c r="C503" t="n">
         <v>134.91</v>
@@ -10532,7 +10532,7 @@
         </is>
       </c>
       <c r="E503" t="n">
-        <v>62.37</v>
+        <v>59.22</v>
       </c>
       <c r="F503" t="inlineStr"/>
     </row>
@@ -10541,7 +10541,7 @@
         <v>45778</v>
       </c>
       <c r="B504" t="n">
-        <v>84.2885</v>
+        <v>81.4701</v>
       </c>
       <c r="C504" t="n">
         <v>127.48</v>
@@ -10552,7 +10552,7 @@
         </is>
       </c>
       <c r="E504" t="n">
-        <v>66.12</v>
+        <v>63.91</v>
       </c>
       <c r="F504" t="inlineStr"/>
     </row>
@@ -10561,7 +10561,7 @@
         <v>45793</v>
       </c>
       <c r="B505" t="n">
-        <v>88.3634</v>
+        <v>86.48860000000001</v>
       </c>
       <c r="C505" t="n">
         <v>127.48</v>
@@ -10572,7 +10572,7 @@
         </is>
       </c>
       <c r="E505" t="n">
-        <v>69.31999999999999</v>
+        <v>67.84</v>
       </c>
       <c r="F505" t="inlineStr"/>
     </row>
@@ -10581,7 +10581,7 @@
         <v>45808</v>
       </c>
       <c r="B506" t="n">
-        <v>87.4432</v>
+        <v>85.4114</v>
       </c>
       <c r="C506" t="n">
         <v>127.48</v>
@@ -10592,7 +10592,7 @@
         </is>
       </c>
       <c r="E506" t="n">
-        <v>68.59</v>
+        <v>67</v>
       </c>
       <c r="F506" t="inlineStr"/>
     </row>
@@ -10601,7 +10601,7 @@
         <v>45823</v>
       </c>
       <c r="B507" t="n">
-        <v>88.803</v>
+        <v>87.3113</v>
       </c>
       <c r="C507" t="n">
         <v>127.48</v>
@@ -10612,7 +10612,7 @@
         </is>
       </c>
       <c r="E507" t="n">
-        <v>69.66</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="F507" t="inlineStr"/>
     </row>
@@ -10621,7 +10621,7 @@
         <v>45838</v>
       </c>
       <c r="B508" t="n">
-        <v>91.9102</v>
+        <v>91.9328</v>
       </c>
       <c r="C508" t="n">
         <v>127.48</v>
@@ -10632,7 +10632,7 @@
         </is>
       </c>
       <c r="E508" t="n">
-        <v>72.09999999999999</v>
+        <v>72.12</v>
       </c>
       <c r="F508" t="inlineStr"/>
     </row>
@@ -10641,7 +10641,7 @@
         <v>45853</v>
       </c>
       <c r="B509" t="n">
-        <v>94.7013</v>
+        <v>95.1726</v>
       </c>
       <c r="C509" t="n">
         <v>127.48</v>
@@ -10652,7 +10652,7 @@
         </is>
       </c>
       <c r="E509" t="n">
-        <v>74.29000000000001</v>
+        <v>74.66</v>
       </c>
       <c r="F509" t="inlineStr"/>
     </row>
@@ -10661,7 +10661,7 @@
         <v>45868</v>
       </c>
       <c r="B510" t="n">
-        <v>99.8034</v>
+        <v>101.3753</v>
       </c>
       <c r="C510" t="n">
         <v>127.48</v>
@@ -10672,7 +10672,7 @@
         </is>
       </c>
       <c r="E510" t="n">
-        <v>78.29000000000001</v>
+        <v>79.52</v>
       </c>
       <c r="F510" t="inlineStr"/>
     </row>
@@ -10681,7 +10681,7 @@
         <v>45883</v>
       </c>
       <c r="B511" t="n">
-        <v>102.1406</v>
+        <v>104.853</v>
       </c>
       <c r="C511" t="n">
         <v>127.48</v>
@@ -10692,7 +10692,7 @@
         </is>
       </c>
       <c r="E511" t="n">
-        <v>80.12</v>
+        <v>82.25</v>
       </c>
       <c r="F511" t="inlineStr"/>
     </row>
@@ -10701,7 +10701,7 @@
         <v>45898</v>
       </c>
       <c r="B512" t="n">
-        <v>110.9646</v>
+        <v>116.8029</v>
       </c>
       <c r="C512" t="n">
         <v>127.48</v>
@@ -10712,7 +10712,7 @@
         </is>
       </c>
       <c r="E512" t="n">
-        <v>87.04000000000001</v>
+        <v>91.62</v>
       </c>
       <c r="F512" t="inlineStr"/>
     </row>
@@ -10721,7 +10721,7 @@
         <v>45913</v>
       </c>
       <c r="B513" t="n">
-        <v>111.5484</v>
+        <v>117.8583</v>
       </c>
       <c r="C513" t="n">
         <v>127.48</v>
@@ -10732,7 +10732,7 @@
         </is>
       </c>
       <c r="E513" t="n">
-        <v>87.5</v>
+        <v>92.45</v>
       </c>
       <c r="F513" t="inlineStr"/>
     </row>
@@ -10741,7 +10741,7 @@
         <v>45928</v>
       </c>
       <c r="B514" t="n">
-        <v>109.5905</v>
+        <v>117.1155</v>
       </c>
       <c r="C514" t="n">
         <v>127.48</v>
@@ -10752,7 +10752,7 @@
         </is>
       </c>
       <c r="E514" t="n">
-        <v>85.97</v>
+        <v>91.87</v>
       </c>
       <c r="F514" t="inlineStr"/>
     </row>
@@ -10761,7 +10761,7 @@
         <v>45943</v>
       </c>
       <c r="B515" t="n">
-        <v>112.4194</v>
+        <v>119.3006</v>
       </c>
       <c r="C515" t="n">
         <v>127.48</v>
@@ -10772,7 +10772,7 @@
         </is>
       </c>
       <c r="E515" t="n">
-        <v>88.19</v>
+        <v>93.58</v>
       </c>
       <c r="F515" t="inlineStr"/>
     </row>
@@ -10781,7 +10781,7 @@
         <v>45958</v>
       </c>
       <c r="B516" t="n">
-        <v>116.9684</v>
+        <v>122.9333</v>
       </c>
       <c r="C516" t="n">
         <v>127.48</v>
@@ -10792,7 +10792,7 @@
         </is>
       </c>
       <c r="E516" t="n">
-        <v>91.75</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="F516" t="inlineStr"/>
     </row>
@@ -10801,7 +10801,7 @@
         <v>45973</v>
       </c>
       <c r="B517" t="n">
-        <v>117.5177</v>
+        <v>122.8689</v>
       </c>
       <c r="C517" t="n">
         <v>127.48</v>
@@ -10812,7 +10812,7 @@
         </is>
       </c>
       <c r="E517" t="n">
-        <v>92.19</v>
+        <v>96.38</v>
       </c>
       <c r="F517" t="inlineStr"/>
     </row>
@@ -10821,7 +10821,7 @@
         <v>45988</v>
       </c>
       <c r="B518" t="n">
-        <v>111.7632</v>
+        <v>116.7155</v>
       </c>
       <c r="C518" t="n">
         <v>127.48</v>
@@ -10832,7 +10832,7 @@
         </is>
       </c>
       <c r="E518" t="n">
-        <v>87.67</v>
+        <v>91.56</v>
       </c>
       <c r="F518" t="inlineStr"/>
     </row>
@@ -10841,7 +10841,7 @@
         <v>46003</v>
       </c>
       <c r="B519" t="n">
-        <v>112.4124</v>
+        <v>118.7549</v>
       </c>
       <c r="C519" t="n">
         <v>127.48</v>
@@ -10852,7 +10852,7 @@
         </is>
       </c>
       <c r="E519" t="n">
-        <v>88.18000000000001</v>
+        <v>93.16</v>
       </c>
       <c r="F519" t="inlineStr"/>
     </row>
@@ -10861,7 +10861,7 @@
         <v>46018</v>
       </c>
       <c r="B520" t="n">
-        <v>115.8376</v>
+        <v>123.3007</v>
       </c>
       <c r="C520" t="n">
         <v>127.48</v>
@@ -10872,7 +10872,7 @@
         </is>
       </c>
       <c r="E520" t="n">
-        <v>90.87</v>
+        <v>96.72</v>
       </c>
       <c r="F520" t="inlineStr"/>
     </row>
@@ -10881,7 +10881,7 @@
         <v>46033</v>
       </c>
       <c r="B521" t="n">
-        <v>123.0608</v>
+        <v>120.6962</v>
       </c>
       <c r="C521" t="n">
         <v>127.48</v>
@@ -10892,7 +10892,7 @@
         </is>
       </c>
       <c r="E521" t="n">
-        <v>96.53</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="F521" t="inlineStr"/>
     </row>
@@ -10901,7 +10901,7 @@
         <v>46048</v>
       </c>
       <c r="B522" t="n">
-        <v>123.622</v>
+        <v>120.0021</v>
       </c>
       <c r="C522" t="n">
         <v>141</v>
@@ -10912,7 +10912,7 @@
         </is>
       </c>
       <c r="E522" t="n">
-        <v>87.68000000000001</v>
+        <v>85.11</v>
       </c>
       <c r="F522" t="inlineStr"/>
     </row>
@@ -10921,7 +10921,7 @@
         <v>46063</v>
       </c>
       <c r="B523" t="n">
-        <v>123.4266</v>
+        <v>120.223</v>
       </c>
       <c r="C523" t="n">
         <v>141</v>
@@ -10932,7 +10932,7 @@
         </is>
       </c>
       <c r="E523" t="n">
-        <v>87.54000000000001</v>
+        <v>85.26000000000001</v>
       </c>
       <c r="F523" t="inlineStr"/>
     </row>
@@ -10941,7 +10941,7 @@
         <v>46078</v>
       </c>
       <c r="B524" t="n">
-        <v>124.2957</v>
+        <v>119.6503</v>
       </c>
       <c r="C524" t="n">
         <v>141</v>
@@ -10952,7 +10952,7 @@
         </is>
       </c>
       <c r="E524" t="n">
-        <v>88.15000000000001</v>
+        <v>84.86</v>
       </c>
       <c r="F524" t="inlineStr"/>
     </row>
@@ -10961,7 +10961,7 @@
         <v>46093</v>
       </c>
       <c r="B525" t="n">
-        <v>123.4603</v>
+        <v>119.9801</v>
       </c>
       <c r="C525" t="n">
         <v>141</v>
@@ -10972,7 +10972,7 @@
         </is>
       </c>
       <c r="E525" t="n">
-        <v>87.56</v>
+        <v>85.09</v>
       </c>
       <c r="F525" t="inlineStr"/>
     </row>
@@ -10981,7 +10981,7 @@
         <v>46108</v>
       </c>
       <c r="B526" t="n">
-        <v>113.5354</v>
+        <v>122.8698</v>
       </c>
       <c r="C526" t="n">
         <v>141</v>
@@ -10992,7 +10992,7 @@
         </is>
       </c>
       <c r="E526" t="n">
-        <v>80.52</v>
+        <v>87.14</v>
       </c>
       <c r="F526" t="inlineStr"/>
     </row>
@@ -11001,7 +11001,7 @@
         <v>46123</v>
       </c>
       <c r="B527" t="n">
-        <v>116.8763</v>
+        <v>121.66</v>
       </c>
       <c r="C527" t="n">
         <v>141</v>
@@ -11012,7 +11012,7 @@
         </is>
       </c>
       <c r="E527" t="n">
-        <v>82.89</v>
+        <v>86.28</v>
       </c>
       <c r="F527" t="inlineStr"/>
     </row>
@@ -11021,7 +11021,7 @@
         <v>46138</v>
       </c>
       <c r="B528" t="n">
-        <v>121.1931</v>
+        <v>120.1307</v>
       </c>
       <c r="C528" t="n">
         <v>141</v>
@@ -11032,7 +11032,7 @@
         </is>
       </c>
       <c r="E528" t="n">
-        <v>85.95</v>
+        <v>85.2</v>
       </c>
       <c r="F528" t="inlineStr"/>
     </row>
@@ -11041,7 +11041,7 @@
         <v>46153</v>
       </c>
       <c r="B529" t="n">
-        <v>127.8803</v>
+        <v>117.3834</v>
       </c>
       <c r="C529" t="n">
         <v>141</v>
@@ -11052,7 +11052,7 @@
         </is>
       </c>
       <c r="E529" t="n">
-        <v>90.7</v>
+        <v>83.25</v>
       </c>
       <c r="F529" t="inlineStr"/>
     </row>
@@ -11061,7 +11061,7 @@
         <v>46168</v>
       </c>
       <c r="B530" t="n">
-        <v>124.21</v>
+        <v>118.4141</v>
       </c>
       <c r="C530" t="n">
         <v>141</v>
@@ -11072,7 +11072,7 @@
         </is>
       </c>
       <c r="E530" t="n">
-        <v>88.09</v>
+        <v>83.98</v>
       </c>
       <c r="F530" t="inlineStr"/>
     </row>
@@ -11081,7 +11081,7 @@
         <v>46183</v>
       </c>
       <c r="B531" t="n">
-        <v>117.1993</v>
+        <v>121.2529</v>
       </c>
       <c r="C531" t="n">
         <v>141</v>
@@ -11092,7 +11092,7 @@
         </is>
       </c>
       <c r="E531" t="n">
-        <v>83.12</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="F531" t="inlineStr"/>
     </row>
@@ -11101,7 +11101,7 @@
         <v>46198</v>
       </c>
       <c r="B532" t="n">
-        <v>123.0538</v>
+        <v>118.5476</v>
       </c>
       <c r="C532" t="n">
         <v>141</v>
@@ -11112,7 +11112,7 @@
         </is>
       </c>
       <c r="E532" t="n">
-        <v>87.27</v>
+        <v>84.08</v>
       </c>
       <c r="F532" t="inlineStr"/>
     </row>
@@ -11121,7 +11121,7 @@
         <v>46213</v>
       </c>
       <c r="B533" t="n">
-        <v>117.3343</v>
+        <v>115.4436</v>
       </c>
       <c r="C533" t="n">
         <v>141</v>
@@ -11132,7 +11132,7 @@
         </is>
       </c>
       <c r="E533" t="n">
-        <v>83.22</v>
+        <v>81.87</v>
       </c>
       <c r="F533" t="inlineStr"/>
     </row>
@@ -11141,7 +11141,7 @@
         <v>46228</v>
       </c>
       <c r="B534" t="n">
-        <v>108.9495</v>
+        <v>109.4555</v>
       </c>
       <c r="C534" t="n">
         <v>141</v>
@@ -11152,7 +11152,7 @@
         </is>
       </c>
       <c r="E534" t="n">
-        <v>77.27</v>
+        <v>77.63</v>
       </c>
       <c r="F534" t="inlineStr"/>
     </row>
